--- a/research/traditional_assets/database/data/turkey/turkey_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_insurance_life.xlsx
@@ -588,49 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.3139999999999999</v>
+        <v>0.5125</v>
       </c>
       <c r="E2">
-        <v>0.513</v>
-      </c>
-      <c r="F2">
-        <v>0.23</v>
+        <v>0.4565</v>
       </c>
       <c r="G2">
-        <v>0.2474625422909618</v>
+        <v>0.1259303012404017</v>
       </c>
       <c r="H2">
-        <v>0.2474625422909618</v>
+        <v>0.1259303012404017</v>
       </c>
       <c r="I2">
-        <v>0.2252295795070082</v>
+        <v>0.1188422917897224</v>
       </c>
       <c r="J2">
-        <v>0.1722514065388261</v>
+        <v>0.09214018130639599</v>
       </c>
       <c r="K2">
-        <v>116.1</v>
+        <v>99</v>
       </c>
       <c r="L2">
-        <v>0.1870468825519574</v>
+        <v>0.1169521559362079</v>
       </c>
       <c r="M2">
-        <v>65</v>
+        <v>24.3</v>
       </c>
       <c r="N2">
-        <v>0.09692812406799881</v>
+        <v>0.02645905923344948</v>
       </c>
       <c r="O2">
-        <v>0.5598621877691645</v>
+        <v>0.2454545454545455</v>
       </c>
       <c r="P2">
-        <v>65</v>
+        <v>24.3</v>
       </c>
       <c r="Q2">
-        <v>0.09692812406799881</v>
+        <v>0.02645905923344948</v>
       </c>
       <c r="R2">
-        <v>0.5598621877691645</v>
+        <v>0.2454545454545455</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +636,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>117.2</v>
+        <v>83.8</v>
       </c>
       <c r="V2">
-        <v>0.1747688637041455</v>
+        <v>0.09124564459930314</v>
       </c>
       <c r="W2">
-        <v>0.548973802704176</v>
+        <v>0.383838474242945</v>
       </c>
       <c r="X2">
-        <v>0.1103604129985723</v>
+        <v>0.1785692899505576</v>
       </c>
       <c r="Y2">
-        <v>0.4386133897056036</v>
+        <v>0.2052691842923874</v>
       </c>
       <c r="Z2">
-        <v>5.731831194016068</v>
+        <v>5.072811170372145</v>
       </c>
       <c r="AA2">
-        <v>-1.169650855229135</v>
+        <v>1.359429413579731</v>
       </c>
       <c r="AB2">
-        <v>0.1095746520563719</v>
+        <v>0.1768767559138295</v>
       </c>
       <c r="AC2">
-        <v>-1.279225507285507</v>
+        <v>1.182552657665901</v>
       </c>
       <c r="AD2">
-        <v>10.67</v>
+        <v>22.15</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10.67</v>
+        <v>22.15</v>
       </c>
       <c r="AG2">
-        <v>-106.53</v>
+        <v>-61.64999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.01566192552145258</v>
+        <v>0.02355005050236564</v>
       </c>
       <c r="AI2">
-        <v>0.03756116450170733</v>
+        <v>0.09670377646802009</v>
       </c>
       <c r="AJ2">
-        <v>-0.1888595387097346</v>
+        <v>-0.07195798074117303</v>
       </c>
       <c r="AK2">
-        <v>-0.6384011505962727</v>
+        <v>-0.4244406196213424</v>
       </c>
       <c r="AL2">
-        <v>0.787</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.787</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.07414871438498957</v>
-      </c>
-      <c r="AO2">
-        <v>177.6365946632783</v>
+        <v>0.2146317829457365</v>
       </c>
       <c r="AP2">
-        <v>-0.7403057678943711</v>
-      </c>
-      <c r="AQ2">
-        <v>177.6365946632783</v>
+        <v>-0.5973837209302325</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anadolu Hayat Emeklilik Anonim Sirketi (IBSE:ANHYT)</t>
+          <t>AgeSA Hayat ve Emeklilik Anonim Sirketi (IBSE:AGESA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,103 +716,100 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.29</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="E3">
-        <v>0.289</v>
+        <v>0.556</v>
       </c>
       <c r="G3">
-        <v>0.261725535610886</v>
+        <v>0.09463647199046485</v>
       </c>
       <c r="H3">
-        <v>0.261725535610886</v>
+        <v>0.09463647199046485</v>
       </c>
       <c r="I3">
-        <v>0.2350897510133179</v>
+        <v>0.08605482717520858</v>
       </c>
       <c r="J3">
-        <v>0.1813222653801017</v>
+        <v>0.06640326443169869</v>
       </c>
       <c r="K3">
-        <v>63.4</v>
+        <v>41.9</v>
       </c>
       <c r="L3">
-        <v>0.1835552982049797</v>
+        <v>0.09988081048867699</v>
       </c>
       <c r="M3">
-        <v>41.5</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1061924257932446</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.6545741324921136</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>41.5</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.1061924257932446</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.6545741324921136</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>34</v>
+        <v>42.3</v>
       </c>
       <c r="V3">
-        <v>0.08700102354145342</v>
+        <v>0.109020618556701</v>
       </c>
       <c r="W3">
-        <v>0.3535973229224763</v>
+        <v>0.4515086206896552</v>
       </c>
       <c r="X3">
-        <v>0.1109198156478622</v>
+        <v>0.1767247243616839</v>
       </c>
       <c r="Y3">
-        <v>0.242677507274614</v>
+        <v>0.2747838963279713</v>
       </c>
       <c r="Z3">
-        <v>2.78750706157695</v>
+        <v>36.07050730868445</v>
       </c>
       <c r="AA3">
-        <v>0.5054370951681633</v>
+        <v>2.395199435004094</v>
       </c>
       <c r="AB3">
-        <v>0.1097348356192283</v>
+        <v>0.1764337034714682</v>
       </c>
       <c r="AC3">
-        <v>0.395702259548935</v>
+        <v>2.218765731532626</v>
       </c>
       <c r="AD3">
-        <v>8.640000000000001</v>
+        <v>1.55</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8.640000000000001</v>
+        <v>1.55</v>
       </c>
       <c r="AG3">
-        <v>-25.36</v>
+        <v>-40.75</v>
       </c>
       <c r="AH3">
-        <v>0.0216302823953535</v>
+        <v>0.003978950070594275</v>
       </c>
       <c r="AI3">
-        <v>0.0456563094483196</v>
+        <v>0.0196078431372549</v>
       </c>
       <c r="AJ3">
-        <v>-0.06939579684763572</v>
+        <v>-0.1173506119510439</v>
       </c>
       <c r="AK3">
-        <v>-0.163359958773512</v>
+        <v>-1.108843537414966</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -830,10 +818,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.1029797377830751</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="AP3">
-        <v>-0.3022646007151371</v>
+        <v>-1.095430107526882</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Agesa Hayat ve Emeklilik A.S. (IBSE:AGESA)</t>
+          <t>Anadolu Hayat Emeklilik Anonim Sirketi (IBSE:ANHYT)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,49 +841,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.338</v>
+        <v>0.459</v>
       </c>
       <c r="E4">
-        <v>0.737</v>
-      </c>
-      <c r="F4">
-        <v>0.23</v>
+        <v>0.357</v>
       </c>
       <c r="G4">
-        <v>0.2295677442789684</v>
+        <v>0.1566744730679157</v>
       </c>
       <c r="H4">
-        <v>0.2295677442789684</v>
+        <v>0.1566744730679157</v>
       </c>
       <c r="I4">
-        <v>0.2128586996004359</v>
+        <v>0.1510538641686183</v>
       </c>
       <c r="J4">
-        <v>0.1614050858840715</v>
+        <v>0.1176695176538623</v>
       </c>
       <c r="K4">
-        <v>52.7</v>
+        <v>57.1</v>
       </c>
       <c r="L4">
-        <v>0.1914275335997094</v>
+        <v>0.1337236533957845</v>
       </c>
       <c r="M4">
-        <v>23.5</v>
+        <v>24.3</v>
       </c>
       <c r="N4">
-        <v>0.08398856325947104</v>
+        <v>0.04581447963800905</v>
       </c>
       <c r="O4">
-        <v>0.4459203036053131</v>
+        <v>0.425569176882662</v>
       </c>
       <c r="P4">
-        <v>23.5</v>
+        <v>24.3</v>
       </c>
       <c r="Q4">
-        <v>0.08398856325947104</v>
+        <v>0.04581447963800905</v>
       </c>
       <c r="R4">
-        <v>0.4459203036053131</v>
+        <v>0.425569176882662</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,73 +889,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>83.2</v>
+        <v>41.5</v>
       </c>
       <c r="V4">
-        <v>0.2973552537526805</v>
+        <v>0.07824283559577677</v>
       </c>
       <c r="W4">
-        <v>0.7443502824858758</v>
+        <v>0.3161683277962348</v>
       </c>
       <c r="X4">
-        <v>0.1098010103492824</v>
+        <v>0.1804138555394312</v>
       </c>
       <c r="Y4">
-        <v>0.6345492721365933</v>
+        <v>0.1357544722568036</v>
       </c>
       <c r="Z4">
-        <v>-17.62483994878361</v>
+        <v>2.750579747487761</v>
       </c>
       <c r="AA4">
-        <v>-2.844738805626433</v>
+        <v>0.3236593921553671</v>
       </c>
       <c r="AB4">
-        <v>0.1094144684935155</v>
+        <v>0.1773198083561907</v>
       </c>
       <c r="AC4">
-        <v>-2.954153274119948</v>
+        <v>0.1463395837991764</v>
       </c>
       <c r="AD4">
-        <v>2.03</v>
+        <v>20.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.03</v>
+        <v>20.6</v>
       </c>
       <c r="AG4">
-        <v>-81.17</v>
+        <v>-20.9</v>
       </c>
       <c r="AH4">
-        <v>0.00720292374835894</v>
+        <v>0.03738656987295826</v>
       </c>
       <c r="AI4">
-        <v>0.02140672782874618</v>
+        <v>0.1373333333333333</v>
       </c>
       <c r="AJ4">
-        <v>-0.4086492473443085</v>
+        <v>-0.04102060843964671</v>
       </c>
       <c r="AK4">
-        <v>-6.979363714531387</v>
+        <v>-0.1926267281105991</v>
       </c>
       <c r="AL4">
-        <v>0.787</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.787</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.03383333333333333</v>
-      </c>
-      <c r="AO4">
-        <v>74.45997458703938</v>
+        <v>0.3121212121212121</v>
       </c>
       <c r="AP4">
-        <v>-1.352833333333333</v>
-      </c>
-      <c r="AQ4">
-        <v>74.45997458703938</v>
+        <v>-0.3166666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/turkey/turkey_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.5125</v>
+        <v>0.6105</v>
       </c>
       <c r="E2">
-        <v>0.4565</v>
+        <v>0.5369999999999999</v>
       </c>
       <c r="G2">
-        <v>0.1259303012404017</v>
+        <v>0.145826964231122</v>
       </c>
       <c r="H2">
-        <v>0.1259303012404017</v>
+        <v>0.145826964231122</v>
       </c>
       <c r="I2">
-        <v>0.1188422917897224</v>
+        <v>0.1628452053398553</v>
       </c>
       <c r="J2">
-        <v>0.09214018130639599</v>
+        <v>0.1268517612209577</v>
       </c>
       <c r="K2">
-        <v>99</v>
+        <v>142.4</v>
       </c>
       <c r="L2">
-        <v>0.1169521559362079</v>
+        <v>0.1451136247834506</v>
       </c>
       <c r="M2">
-        <v>24.3</v>
+        <v>24.05</v>
       </c>
       <c r="N2">
-        <v>0.02645905923344948</v>
+        <v>0.02598314606741573</v>
       </c>
       <c r="O2">
-        <v>0.2454545454545455</v>
+        <v>0.1688904494382022</v>
       </c>
       <c r="P2">
-        <v>24.3</v>
+        <v>24.05</v>
       </c>
       <c r="Q2">
-        <v>0.02645905923344948</v>
+        <v>0.02598314606741573</v>
       </c>
       <c r="R2">
-        <v>0.2454545454545455</v>
+        <v>0.1688904494382022</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,67 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>83.8</v>
+        <v>126.4</v>
       </c>
       <c r="V2">
-        <v>0.09124564459930314</v>
+        <v>0.1365600691443388</v>
       </c>
       <c r="W2">
-        <v>0.383838474242945</v>
+        <v>0.6692626015854813</v>
       </c>
       <c r="X2">
-        <v>0.1785692899505576</v>
+        <v>0.1515315365489974</v>
       </c>
       <c r="Y2">
-        <v>0.2052691842923874</v>
+        <v>0.5177310650364839</v>
       </c>
       <c r="Z2">
-        <v>5.072811170372145</v>
+        <v>6.755938037865748</v>
       </c>
       <c r="AA2">
-        <v>1.359429413579731</v>
+        <v>0.9007610941560789</v>
       </c>
       <c r="AB2">
-        <v>0.1768767559138295</v>
+        <v>0.1495023964529758</v>
       </c>
       <c r="AC2">
-        <v>1.182552657665901</v>
+        <v>0.7512586977031031</v>
       </c>
       <c r="AD2">
-        <v>22.15</v>
+        <v>38.67</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>22.15</v>
+        <v>38.67</v>
       </c>
       <c r="AG2">
-        <v>-61.64999999999999</v>
+        <v>-87.73</v>
       </c>
       <c r="AH2">
-        <v>0.02355005050236564</v>
+        <v>0.04010287575056779</v>
       </c>
       <c r="AI2">
-        <v>0.09670377646802009</v>
+        <v>0.1138457915035181</v>
       </c>
       <c r="AJ2">
-        <v>-0.07195798074117303</v>
+        <v>-0.1047059806413883</v>
       </c>
       <c r="AK2">
-        <v>-0.4244406196213424</v>
+        <v>-0.4113564964598866</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.653</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.653</v>
       </c>
       <c r="AN2">
-        <v>0.2146317829457365</v>
+        <v>0.2400372439478585</v>
+      </c>
+      <c r="AO2">
+        <v>244.7166921898928</v>
       </c>
       <c r="AP2">
-        <v>-0.5973837209302325</v>
+        <v>-0.544568590937306</v>
+      </c>
+      <c r="AQ2">
+        <v>244.7166921898928</v>
       </c>
     </row>
     <row r="3">
@@ -716,100 +722,103 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.5660000000000001</v>
+        <v>0.677</v>
       </c>
       <c r="E3">
-        <v>0.556</v>
+        <v>0.48</v>
       </c>
       <c r="G3">
-        <v>0.09463647199046485</v>
+        <v>0.120858113848768</v>
       </c>
       <c r="H3">
-        <v>0.09463647199046485</v>
+        <v>0.120858113848768</v>
       </c>
       <c r="I3">
-        <v>0.08605482717520858</v>
+        <v>0.09898045879354291</v>
       </c>
       <c r="J3">
-        <v>0.06640326443169869</v>
+        <v>0.0775656065503062</v>
       </c>
       <c r="K3">
-        <v>41.9</v>
+        <v>46</v>
       </c>
       <c r="L3">
-        <v>0.09988081048867699</v>
+        <v>0.09770603228547153</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>5.15</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01385898815931109</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.1119565217391304</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>5.15</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01385898815931109</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.1119565217391304</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>42.3</v>
+        <v>59.4</v>
       </c>
       <c r="V3">
-        <v>0.109020618556701</v>
+        <v>0.1598493003229279</v>
       </c>
       <c r="W3">
-        <v>0.4515086206896552</v>
+        <v>0.5935483870967742</v>
       </c>
       <c r="X3">
-        <v>0.1767247243616839</v>
+        <v>0.1489295113578381</v>
       </c>
       <c r="Y3">
-        <v>0.2747838963279713</v>
+        <v>0.444618875738936</v>
       </c>
       <c r="Z3">
-        <v>36.07050730868445</v>
+        <v>12.8108843537415</v>
       </c>
       <c r="AA3">
-        <v>2.395199435004094</v>
+        <v>0.9936840153437866</v>
       </c>
       <c r="AB3">
-        <v>0.1764337034714682</v>
+        <v>0.1487022292183455</v>
       </c>
       <c r="AC3">
-        <v>2.218765731532626</v>
+        <v>0.8449817861254411</v>
       </c>
       <c r="AD3">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AG3">
-        <v>-40.75</v>
+        <v>-57.93</v>
       </c>
       <c r="AH3">
-        <v>0.003978950070594275</v>
+        <v>0.003940279304152035</v>
       </c>
       <c r="AI3">
-        <v>0.0196078431372549</v>
+        <v>0.01564329041183356</v>
       </c>
       <c r="AJ3">
-        <v>-0.1173506119510439</v>
+        <v>-0.1846845410782032</v>
       </c>
       <c r="AK3">
-        <v>-1.108843537414966</v>
+        <v>-1.675730402082731</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -818,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.04166666666666666</v>
+        <v>0.0310126582278481</v>
       </c>
       <c r="AP3">
-        <v>-1.095430107526882</v>
+        <v>-1.222151898734177</v>
       </c>
     </row>
     <row r="4">
@@ -841,46 +850,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.459</v>
+        <v>0.544</v>
       </c>
       <c r="E4">
-        <v>0.357</v>
+        <v>0.594</v>
       </c>
       <c r="G4">
-        <v>0.1566744730679157</v>
+        <v>0.1688540646425074</v>
       </c>
       <c r="H4">
-        <v>0.1566744730679157</v>
+        <v>0.1688540646425074</v>
       </c>
       <c r="I4">
-        <v>0.1510538641686183</v>
+        <v>0.221743388834476</v>
       </c>
       <c r="J4">
-        <v>0.1176695176538623</v>
+        <v>0.1716952825995461</v>
       </c>
       <c r="K4">
-        <v>57.1</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="L4">
-        <v>0.1337236533957845</v>
+        <v>0.1888344760039177</v>
       </c>
       <c r="M4">
-        <v>24.3</v>
+        <v>18.9</v>
       </c>
       <c r="N4">
-        <v>0.04581447963800905</v>
+        <v>0.03411552346570397</v>
       </c>
       <c r="O4">
-        <v>0.425569176882662</v>
+        <v>0.196058091286307</v>
       </c>
       <c r="P4">
-        <v>24.3</v>
+        <v>18.9</v>
       </c>
       <c r="Q4">
-        <v>0.04581447963800905</v>
+        <v>0.03411552346570397</v>
       </c>
       <c r="R4">
-        <v>0.425569176882662</v>
+        <v>0.196058091286307</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,67 +898,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>41.5</v>
+        <v>67</v>
       </c>
       <c r="V4">
-        <v>0.07824283559577677</v>
+        <v>0.1209386281588448</v>
       </c>
       <c r="W4">
-        <v>0.3161683277962348</v>
+        <v>0.7449768160741885</v>
       </c>
       <c r="X4">
-        <v>0.1804138555394312</v>
+        <v>0.1541335617401566</v>
       </c>
       <c r="Y4">
-        <v>0.1357544722568036</v>
+        <v>0.590843254334032</v>
       </c>
       <c r="Z4">
-        <v>2.750579747487761</v>
+        <v>4.705069124423964</v>
       </c>
       <c r="AA4">
-        <v>0.3236593921553671</v>
+        <v>0.8078381729683711</v>
       </c>
       <c r="AB4">
-        <v>0.1773198083561907</v>
+        <v>0.1503025636876061</v>
       </c>
       <c r="AC4">
-        <v>0.1463395837991764</v>
+        <v>0.657535609280765</v>
       </c>
       <c r="AD4">
-        <v>20.6</v>
+        <v>37.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>20.6</v>
+        <v>37.2</v>
       </c>
       <c r="AG4">
-        <v>-20.9</v>
+        <v>-29.8</v>
       </c>
       <c r="AH4">
-        <v>0.03738656987295826</v>
+        <v>0.06292286874154263</v>
       </c>
       <c r="AI4">
-        <v>0.1373333333333333</v>
+        <v>0.1514041514041514</v>
       </c>
       <c r="AJ4">
-        <v>-0.04102060843964671</v>
+        <v>-0.0568485310950019</v>
       </c>
       <c r="AK4">
-        <v>-0.1926267281105991</v>
+        <v>-0.1667599328483492</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.653</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.653</v>
       </c>
       <c r="AN4">
-        <v>0.3121212121212121</v>
+        <v>0.3271767810026385</v>
+      </c>
+      <c r="AO4">
+        <v>173.353751914242</v>
       </c>
       <c r="AP4">
-        <v>-0.3166666666666667</v>
+        <v>-0.2620932277924362</v>
+      </c>
+      <c r="AQ4">
+        <v>173.353751914242</v>
       </c>
     </row>
   </sheetData>
